--- a/TOR330 Data/4. TOR330 Timetable Data/TOR330_lifebase_cut_offs_df.xlsx
+++ b/TOR330 Data/4. TOR330 Timetable Data/TOR330_lifebase_cut_offs_df.xlsx
@@ -626,7 +626,7 @@
         <v>12050</v>
       </c>
       <c r="G6">
-        <v>64800.00000000001</v>
+        <v>64800</v>
       </c>
       <c r="H6">
         <v>223200</v>
@@ -730,7 +730,7 @@
         <v>21077</v>
       </c>
       <c r="G10">
-        <v>64800.00000000001</v>
+        <v>64800</v>
       </c>
       <c r="H10">
         <v>378000</v>
